--- a/sobeys_receipt_items_categorized.xlsx
+++ b/sobeys_receipt_items_categorized.xlsx
@@ -433,16 +433,19 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G62"/>
+  <dimension ref="A1:J66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
     <col width="9" customWidth="1" min="2" max="2"/>
     <col width="23" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="17" customWidth="1" min="5" max="5"/>
-    <col width="17" customWidth="1" min="6" max="6"/>
-    <col width="34" customWidth="1" min="7" max="7"/>
+    <col width="6" customWidth="1" min="5" max="5"/>
+    <col width="21" customWidth="1" min="6" max="6"/>
+    <col width="21" customWidth="1" min="7" max="7"/>
+    <col width="17" customWidth="1" min="8" max="8"/>
+    <col width="17" customWidth="1" min="9" max="9"/>
+    <col width="53" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -468,15 +471,30 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
+          <t>Code</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>GST</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>PST</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
           <t>budget_category</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>category_source</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>raw_line</t>
         </is>
@@ -489,31 +507,38 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Pie Filling S/Berry</t>
+          <t>Comp Quick Oats 1KG</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>6.49</v>
+        <v>4.79</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Groceries</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>Gep Pic Med | $6.49</t>
-        </is>
-      </c>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="F2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Groceries</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -522,31 +547,38 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Pie Filling S/Berry</t>
+          <t>Vinta Crackers</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>6.49</v>
+        <v>4.29</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Groceries</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
+          <t>C</t>
+        </is>
+      </c>
+      <c r="F3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Groceries</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
         <is>
           <t>exact</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>Cep Pic Med | $6.49</t>
-        </is>
-      </c>
+      <c r="J3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -555,31 +587,38 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Pie Filling S/Berry</t>
+          <t>Candy GMS Org</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>6.49</v>
+        <v>3.49</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Groceries</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
+          <t>BC</t>
+        </is>
+      </c>
+      <c r="F4" t="n">
+        <v>0.1745</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.2443</v>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Groceries</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
         <is>
           <t>exact</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>Pie Filling S/Berry | $6.49</t>
-        </is>
-      </c>
+      <c r="J4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -588,11 +627,11 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>23</v>
+        <v>3</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Pie Filling S/Berry</t>
+          <t>Oep Pic Med</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -600,17 +639,28 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Groceries</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>Pie Filling S/Berry | $6.49</t>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="F5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Groceries</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>GROCERY | $6.49</t>
         </is>
       </c>
     </row>
@@ -621,29 +671,40 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>31</v>
+        <v>9</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Pretzels HoneyMustar</t>
+          <t>Oep Pic Med</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>5.49</v>
+        <v>5.99</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Groceries</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
+          <t>C</t>
+        </is>
+      </c>
+      <c r="F6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Groceries</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
         <is>
           <t>default</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>200 PTS | $5.49 BC</t>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>Cep Pic Med | $6.49 | INSTANT SAVINGS -0.50</t>
         </is>
       </c>
     </row>
@@ -654,29 +715,40 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>37</v>
+        <v>13</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Pretzels HoneyMustar</t>
+          <t>Pie Filling S/Berry</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>1</v>
+        <v>5.99</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Groceries</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>default</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>Pretzels HoneyMustar | $1.00 |</t>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="F7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Groceries</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>Pie Filling S/Berry | $6.49 | INSTANT SAVINGS -0.50</t>
         </is>
       </c>
     </row>
@@ -687,29 +759,40 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>43</v>
+        <v>23</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Pretzel Cracker Rahe</t>
+          <t>Pie Filling S/Berry</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>5.49</v>
+        <v>6.49</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Groceries</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
+          <t>C</t>
+        </is>
+      </c>
+      <c r="F8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Groceries</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
         <is>
           <t>exact</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>Pretzel Cracker Rahe | $5.49 BC</t>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>Pie Filling S/Berry | $6.49</t>
         </is>
       </c>
     </row>
@@ -720,29 +803,40 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>51</v>
+        <v>37</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Chips Rstrnt Sty Lin</t>
+          <t>Pretzels HoneyMustar</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>5.29</v>
+        <v>5.49</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Groceries</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>Chips Multigrai | $5.29 BC</t>
+          <t>BC</t>
+        </is>
+      </c>
+      <c r="F9" t="n">
+        <v>0.2745</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.3843</v>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Groceries</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>Pretzels HoneyMustar | $1.00 |</t>
         </is>
       </c>
     </row>
@@ -753,29 +847,40 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>69</v>
+        <v>43</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Comp Quick Oats 1KG</t>
+          <t>Pretzel Cracker Rach</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>4.79</v>
+        <v>5.49</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Groceries</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>default</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>YOU SAV | $4.79</t>
+          <t>BC</t>
+        </is>
+      </c>
+      <c r="F10" t="n">
+        <v>0.2745</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.3843</v>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Groceries</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>Pretzel Cracker Rahe | $5.49 BC</t>
         </is>
       </c>
     </row>
@@ -786,29 +891,40 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>81</v>
+        <v>51</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Gloves Cmfrt Med 1EA</t>
+          <t>Chips Multigrain</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>4.29</v>
+        <v>5.29</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Clothing</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
+          <t>BC</t>
+        </is>
+      </c>
+      <c r="F11" t="n">
+        <v>0.2645</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.3703</v>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Groceries</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
         <is>
           <t>exact</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>Vinta Crackers | $4.29</t>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>Chips Multigrai | $5.29 BC</t>
         </is>
       </c>
     </row>
@@ -819,29 +935,40 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Pepsi Zero</t>
+          <t>Chips Rstrnt Sty Lm</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>4.25</v>
+        <v>5.29</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Groceries</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
+          <t>BC</t>
+        </is>
+      </c>
+      <c r="F12" t="n">
+        <v>0.2645</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0.3703</v>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Groceries</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
         <is>
           <t>default</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>Pepsi Zero | $4.25</t>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>C | $4.29</t>
         </is>
       </c>
     </row>
@@ -852,29 +979,40 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>97</v>
+        <v>85</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Pepsi Zero</t>
+          <t>Dil Pkls Xt Grlc Snd</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>4.25</v>
+        <v>4.99</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Groceries</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
+          <t>C</t>
+        </is>
+      </c>
+      <c r="F13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Groceries</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
         <is>
           <t>default</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>Pepsi Zero | $4.25 BC</t>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>BC | $4.25</t>
         </is>
       </c>
     </row>
@@ -885,29 +1023,40 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>109</v>
+        <v>97</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>English Muffins Sour</t>
+          <t>Pepsi Zero</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>3.49</v>
+        <v>4.37</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Groceries</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>Candy GMS Org | $3.49 BC</t>
+          <t>BC</t>
+        </is>
+      </c>
+      <c r="F14" t="n">
+        <v>0.2125</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0.2975</v>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Groceries</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>Pepsi Zero | $4.25 BC | EHC 0.12</t>
         </is>
       </c>
     </row>
@@ -918,29 +1067,40 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>115</v>
+        <v>97</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>English Muffins Sour</t>
+          <t>Pepsi Zero</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>3.49</v>
+        <v>4.37</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Groceries</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>Candy GMS Ors | $3.49 BC</t>
+          <t>BC</t>
+        </is>
+      </c>
+      <c r="F15" t="n">
+        <v>0.2125</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0.2975</v>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Groceries</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>Pepsi Zero | $4.25 BC | EHC 0.12</t>
         </is>
       </c>
     </row>
@@ -951,29 +1111,40 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>123</v>
+        <v>107</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>English Muffins Sour</t>
+          <t>Mexican Hot Sauce</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>3.49</v>
+        <v>3.69</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Groceries</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
+          <t>C</t>
+        </is>
+      </c>
+      <c r="F16" t="n">
+        <v>0</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0</v>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Groceries</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
         <is>
           <t>exact</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>Candy GMS Or¢ | $3.49 BC</t>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>Mexican Hot Sauce | $3.49 BC</t>
         </is>
       </c>
     </row>
@@ -984,29 +1155,40 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>131</v>
+        <v>115</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Lindor 3Pk</t>
+          <t>Candy GMS Org</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>2.99</v>
+        <v>3.49</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Groceries</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>default</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>Lindor 3Pk | $2.99 BC</t>
+          <t>BC</t>
+        </is>
+      </c>
+      <c r="F17" t="n">
+        <v>0.1745</v>
+      </c>
+      <c r="G17" t="n">
+        <v>0.2443</v>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Groceries</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>Candy GMS Ors | $3.49 BC</t>
         </is>
       </c>
     </row>
@@ -1017,29 +1199,40 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>135</v>
+        <v>123</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Lindor 3Pk</t>
+          <t>Candy GMS Org</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>2.99</v>
+        <v>3.49</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Groceries</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>default</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>Lindor 3Pk | $2.99 BC</t>
+          <t>BC</t>
+        </is>
+      </c>
+      <c r="F18" t="n">
+        <v>0.1745</v>
+      </c>
+      <c r="G18" t="n">
+        <v>0.2443</v>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Groceries</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>Candy GMS Or¢ | $3.49 BC</t>
         </is>
       </c>
     </row>
@@ -1050,7 +1243,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>139</v>
+        <v>131</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -1062,17 +1255,28 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Groceries</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
+          <t>BC</t>
+        </is>
+      </c>
+      <c r="F19" t="n">
+        <v>0.1495</v>
+      </c>
+      <c r="G19" t="n">
+        <v>0.2093</v>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Groceries</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
         <is>
           <t>default</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>Lindor 3Pk | $2.99 ps</t>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>Lindor 3Pk | $2.99 BC</t>
         </is>
       </c>
     </row>
@@ -1083,29 +1287,40 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>143</v>
+        <v>135</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Chicken Broth</t>
+          <t>Lindor 3Pk</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>2.89</v>
+        <v>2.99</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Groceries</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>Chicken Broth | $2.89</t>
+          <t>BC</t>
+        </is>
+      </c>
+      <c r="F20" t="n">
+        <v>0.1495</v>
+      </c>
+      <c r="G20" t="n">
+        <v>0.2093</v>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Groceries</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>Lindor 3Pk | $2.99 BC</t>
         </is>
       </c>
     </row>
@@ -1116,29 +1331,40 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>147</v>
+        <v>139</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Bush Baked Beans</t>
+          <t>Lindor 3Pk</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>2.5</v>
+        <v>2.99</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Groceries</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>Bush Baked Beans | $2.50</t>
+          <t>BC</t>
+        </is>
+      </c>
+      <c r="F21" t="n">
+        <v>0.1495</v>
+      </c>
+      <c r="G21" t="n">
+        <v>0.2093</v>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Groceries</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>Lindor 3Pk | $2.99 ps</t>
         </is>
       </c>
     </row>
@@ -1149,29 +1375,40 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>157</v>
+        <v>143</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Bush Baked Beans</t>
+          <t>Chicken Broth</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>2.5</v>
+        <v>2.89</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Groceries</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr">
+          <t>C</t>
+        </is>
+      </c>
+      <c r="F22" t="n">
+        <v>0</v>
+      </c>
+      <c r="G22" t="n">
+        <v>0</v>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Groceries</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
         <is>
           <t>exact</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>Baked Beans | $2.50</t>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>Chicken Broth | $2.89</t>
         </is>
       </c>
     </row>
@@ -1182,29 +1419,40 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>167</v>
+        <v>147</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Cake Mx CarrotSprmst</t>
+          <t>Bush Baked Beans</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>2.49</v>
+        <v>2.5</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Groceries</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>default</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>Green Relish | $2.49</t>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="F23" t="n">
+        <v>0</v>
+      </c>
+      <c r="G23" t="n">
+        <v>0</v>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Groceries</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>Bush Baked Beans | $2.50</t>
         </is>
       </c>
     </row>
@@ -1215,29 +1463,40 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>175</v>
+        <v>157</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Cake Mx CarrotSprmst</t>
+          <t>Baked Beans</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>2.49</v>
+        <v>2.5</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Groceries</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>default</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>Cake Mx CarrotSprimst | $2.49</t>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="F24" t="n">
+        <v>0</v>
+      </c>
+      <c r="G24" t="n">
+        <v>0</v>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Groceries</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>Baked Beans | $2.50</t>
         </is>
       </c>
     </row>
@@ -1248,11 +1507,11 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>185</v>
+        <v>167</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Cake Mix French Van</t>
+          <t>Green Relish</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1260,17 +1519,28 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Groceries</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr">
+          <t>C</t>
+        </is>
+      </c>
+      <c r="F25" t="n">
+        <v>0</v>
+      </c>
+      <c r="G25" t="n">
+        <v>0</v>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Groceries</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
         <is>
           <t>default</t>
         </is>
       </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>Cake Mix French Van | $2.49</t>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>Green Relish | $2.49</t>
         </is>
       </c>
     </row>
@@ -1281,29 +1551,40 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>193</v>
+        <v>175</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Licorice S/Berry</t>
+          <t>Cake Mx CarrotSprmst</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>1.79</v>
+        <v>2.49</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Groceries</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>Licorice $/Berry | $1.79 BC</t>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="F26" t="n">
+        <v>0</v>
+      </c>
+      <c r="G26" t="n">
+        <v>0</v>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Groceries</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>Cake Mx CarrotSprimst | $2.49</t>
         </is>
       </c>
     </row>
@@ -1314,29 +1595,40 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>197</v>
+        <v>185</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Licorice S/Berry</t>
+          <t>Cake Mix French Van</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>1.79</v>
+        <v>2.49</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Groceries</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>Licorice S/Berry | $1.79 BC</t>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="F27" t="n">
+        <v>0</v>
+      </c>
+      <c r="G27" t="n">
+        <v>0</v>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Groceries</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>Cake Mix French Van | $2.49</t>
         </is>
       </c>
     </row>
@@ -1347,7 +1639,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>201</v>
+        <v>193</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -1359,17 +1651,28 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Groceries</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr">
+          <t>BC</t>
+        </is>
+      </c>
+      <c r="F28" t="n">
+        <v>0.08950000000000001</v>
+      </c>
+      <c r="G28" t="n">
+        <v>0.1253</v>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Groceries</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
         <is>
           <t>exact</t>
         </is>
       </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>Licorice S/Berry | $1.79 BC</t>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>Licorice $/Berry | $1.79 BC</t>
         </is>
       </c>
     </row>
@@ -1380,29 +1683,40 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>205</v>
+        <v>197</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Gloves Cmfrt Med 1EA</t>
+          <t>Licorice S/Berry</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>4.29</v>
+        <v>1.79</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Clothing</t>
-        </is>
-      </c>
-      <c r="F29" t="inlineStr">
+          <t>BC</t>
+        </is>
+      </c>
+      <c r="F29" t="n">
+        <v>0.08950000000000001</v>
+      </c>
+      <c r="G29" t="n">
+        <v>0.1253</v>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Groceries</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
         <is>
           <t>exact</t>
         </is>
       </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>Gloves Cmfrt Med 1EA | $4.29 BC</t>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>Licorice S/Berry | $1.79 BC</t>
         </is>
       </c>
     </row>
@@ -1413,29 +1727,40 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>209</v>
+        <v>201</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Gloves Cmnfrt Med 1EA</t>
+          <t>Licorice S/Berry</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>4.29</v>
+        <v>1.79</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Clothing</t>
-        </is>
-      </c>
-      <c r="F30" t="inlineStr">
+          <t>BC</t>
+        </is>
+      </c>
+      <c r="F30" t="n">
+        <v>0.08950000000000001</v>
+      </c>
+      <c r="G30" t="n">
+        <v>0.1253</v>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Groceries</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
         <is>
           <t>exact</t>
         </is>
       </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>Gloves Cmnfrt Med 1EA | $4.29 BC</t>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>Licorice S/Berry | $1.79 BC</t>
         </is>
       </c>
     </row>
@@ -1446,29 +1771,40 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>213</v>
+        <v>205</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>“Mexican Hot Sauce</t>
+          <t>Gloves Cmfrt Med 1EA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>3.69</v>
+        <v>4.29</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Groceries</t>
-        </is>
-      </c>
-      <c r="F31" t="inlineStr">
+          <t>BC</t>
+        </is>
+      </c>
+      <c r="F31" t="n">
+        <v>0.2145</v>
+      </c>
+      <c r="G31" t="n">
+        <v>0.3003</v>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Clothing</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
         <is>
           <t>exact</t>
         </is>
       </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>Scourer Refill] 1EA | $3.69 BC</t>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>Gloves Cmfrt Med 1EA | $4.29 BC</t>
         </is>
       </c>
     </row>
@@ -1479,29 +1815,40 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>217</v>
+        <v>209</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Butter Sticks Unsltd</t>
+          <t>Gloves Cmnfrt Med 1EA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>8.49</v>
+        <v>4.29</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Groceries</t>
-        </is>
-      </c>
-      <c r="F32" t="inlineStr">
+          <t>BC</t>
+        </is>
+      </c>
+      <c r="F32" t="n">
+        <v>0.2145</v>
+      </c>
+      <c r="G32" t="n">
+        <v>0.3003</v>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>Clothing</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
         <is>
           <t>exact</t>
         </is>
       </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>Butter Sticks Unsltd | $8.49</t>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>Gloves Cmnfrt Med 1EA | $4.29 BC</t>
         </is>
       </c>
     </row>
@@ -1512,29 +1859,40 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>227</v>
+        <v>213</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Sour Cream Light</t>
+          <t>Scourer Refill 1EA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>4.89</v>
+        <v>3.69</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Groceries</t>
-        </is>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>Sour Cream Light | $4.89</t>
+          <t>BC</t>
+        </is>
+      </c>
+      <c r="F33" t="n">
+        <v>0.1845</v>
+      </c>
+      <c r="G33" t="n">
+        <v>0.2583</v>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Groceries</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>Scourer Refill] 1EA | $3.69 BC</t>
         </is>
       </c>
     </row>
@@ -1545,29 +1903,40 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>235</v>
+        <v>217</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Topping Dessert 1L</t>
+          <t>Butter Sticks Unsltd</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>5.99</v>
+        <v>8.49</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Clothing</t>
-        </is>
-      </c>
-      <c r="F34" t="inlineStr">
+          <t>C</t>
+        </is>
+      </c>
+      <c r="F34" t="n">
+        <v>0</v>
+      </c>
+      <c r="G34" t="n">
+        <v>0</v>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>Groceries</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
         <is>
           <t>exact</t>
         </is>
       </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>eon tr 2 uescort aE | $5.99</t>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>Butter Sticks Unsltd | $8.49</t>
         </is>
       </c>
     </row>
@@ -1578,29 +1947,40 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>241</v>
+        <v>223</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Apples Honeycrisp</t>
+          <t>Cottage Cheese 1%MF</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>11.22</v>
+        <v>6.49</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Groceries</t>
-        </is>
-      </c>
-      <c r="F35" t="inlineStr">
+          <t>C</t>
+        </is>
+      </c>
+      <c r="F35" t="n">
+        <v>0</v>
+      </c>
+      <c r="G35" t="n">
+        <v>0</v>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>Groceries</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
         <is>
           <t>exact</t>
         </is>
       </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>piglet foeycr en | $11.22</t>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>Cottage Cheese 1%MF | $6.49</t>
         </is>
       </c>
     </row>
@@ -1611,29 +1991,40 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>253</v>
+        <v>227</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Mango Spears</t>
+          <t>Sour Cream Light</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>8.99</v>
+        <v>4.89</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Groceries</t>
-        </is>
-      </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>default</t>
-        </is>
-      </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>Mango ale | $8.99</t>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="F36" t="n">
+        <v>0</v>
+      </c>
+      <c r="G36" t="n">
+        <v>0</v>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Groceries</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>Sour Cream Light | $4.89</t>
         </is>
       </c>
     </row>
@@ -1644,29 +2035,40 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>257</v>
+        <v>231</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Cheese Feta Light</t>
+          <t>Cottage Cheese 1%MF</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>6.99</v>
+        <v>4.79</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Groceries</t>
-        </is>
-      </c>
-      <c r="F37" t="inlineStr">
+          <t>C</t>
+        </is>
+      </c>
+      <c r="F37" t="n">
+        <v>0</v>
+      </c>
+      <c r="G37" t="n">
+        <v>0</v>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>Groceries</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
         <is>
           <t>exact</t>
         </is>
       </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>Basil Freeze Drd 8G | $6.99</t>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>Cottage Cheese 1%MF | $4.79</t>
         </is>
       </c>
     </row>
@@ -1677,29 +2079,40 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>261</v>
+        <v>235</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Cheese Feta Light</t>
+          <t>Topping Dessert 1L</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>6.99</v>
+        <v>5.99</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Groceries</t>
-        </is>
-      </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>Dill Freeze Ord 10G | $6.99</t>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="F38" t="n">
+        <v>0</v>
+      </c>
+      <c r="G38" t="n">
+        <v>0</v>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>Groceries</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>eon tr 2 uescort aE | $5.99</t>
         </is>
       </c>
     </row>
@@ -1710,29 +2123,40 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>265</v>
+        <v>239</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Pie Filling S/Berry</t>
+          <t>Apples Honeycrisp</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>6.49</v>
+        <v>11.22</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Groceries</t>
-        </is>
-      </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="G39" t="inlineStr">
-        <is>
-          <t>Asparagus | $6.49</t>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="F39" t="n">
+        <v>0</v>
+      </c>
+      <c r="G39" t="n">
+        <v>0</v>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>Groceries</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>PRO | $11.22</t>
         </is>
       </c>
     </row>
@@ -1743,29 +2167,40 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>289</v>
+        <v>253</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Dil Pkls Xt Grle Snd</t>
+          <t>Mango Spears</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>4.99</v>
+        <v>8.99</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Groceries</t>
-        </is>
-      </c>
-      <c r="F40" t="inlineStr">
+          <t>C</t>
+        </is>
+      </c>
+      <c r="F40" t="n">
+        <v>0</v>
+      </c>
+      <c r="G40" t="n">
+        <v>0</v>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>Groceries</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
         <is>
           <t>default</t>
         </is>
       </c>
-      <c r="G40" t="inlineStr">
-        <is>
-          <t>Little Yellows | $4.99</t>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>Mango ale | $8.99</t>
         </is>
       </c>
     </row>
@@ -1776,29 +2211,40 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>295</v>
+        <v>257</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Dil Pkls Xt Grle Snd</t>
+          <t>Basil Freeze Drd 8G</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>4.99</v>
+        <v>6.99</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Groceries</t>
-        </is>
-      </c>
-      <c r="F41" t="inlineStr">
+          <t>C</t>
+        </is>
+      </c>
+      <c r="F41" t="n">
+        <v>0</v>
+      </c>
+      <c r="G41" t="n">
+        <v>0</v>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>Groceries</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
         <is>
           <t>default</t>
         </is>
       </c>
-      <c r="G41" t="inlineStr">
-        <is>
-          <t>Carrots | $4.99</t>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>Basil Freeze Drd 8G | $6.99</t>
         </is>
       </c>
     </row>
@@ -1809,29 +2255,40 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>299</v>
+        <v>261</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Onions Green</t>
+          <t>Dill Freeze Ord 10G</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>3.58</v>
+        <v>6.99</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Groceries</t>
-        </is>
-      </c>
-      <c r="F42" t="inlineStr">
+          <t>C</t>
+        </is>
+      </c>
+      <c r="F42" t="n">
+        <v>0</v>
+      </c>
+      <c r="G42" t="n">
+        <v>0</v>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>Groceries</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
         <is>
           <t>default</t>
         </is>
       </c>
-      <c r="G42" t="inlineStr">
-        <is>
-          <t>Cnions Green | $3.58</t>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>Dill Freeze Ord 10G | $6.99</t>
         </is>
       </c>
     </row>
@@ -1842,29 +2299,40 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>309</v>
+        <v>265</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Cabbage Green</t>
+          <t>Asparagus</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>3.28</v>
+        <v>6.49</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Groceries</t>
-        </is>
-      </c>
-      <c r="F43" t="inlineStr">
+          <t>C</t>
+        </is>
+      </c>
+      <c r="F43" t="n">
+        <v>0</v>
+      </c>
+      <c r="G43" t="n">
+        <v>0</v>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>Groceries</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
         <is>
           <t>default</t>
         </is>
       </c>
-      <c r="G43" t="inlineStr">
-        <is>
-          <t>Cabbage Green | $3.28</t>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>Asparagus | $6.49</t>
         </is>
       </c>
     </row>
@@ -1875,29 +2343,40 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>323</v>
+        <v>277</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Bananas</t>
+          <t>Org Straws</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>2.42</v>
+        <v>6.49</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Groceries</t>
-        </is>
-      </c>
-      <c r="F44" t="inlineStr">
+          <t>C</t>
+        </is>
+      </c>
+      <c r="F44" t="n">
+        <v>0</v>
+      </c>
+      <c r="G44" t="n">
+        <v>0</v>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>Groceries</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
         <is>
           <t>exact</t>
         </is>
       </c>
-      <c r="G44" t="inlineStr">
-        <is>
-          <t>Bananas | $2.42</t>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>Org Straws | $6.49</t>
         </is>
       </c>
     </row>
@@ -1908,29 +2387,40 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>331</v>
+        <v>283</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>oniahe ae</t>
+          <t>Strawberries 1lb</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>2.3</v>
+        <v>6.49</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Groceries</t>
-        </is>
-      </c>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t>default</t>
-        </is>
-      </c>
-      <c r="G45" t="inlineStr">
-        <is>
-          <t>oniahe ae | $2.30</t>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="F45" t="n">
+        <v>0</v>
+      </c>
+      <c r="G45" t="n">
+        <v>0</v>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>Groceries</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>Strawberries 11b | $6.49</t>
         </is>
       </c>
     </row>
@@ -1941,29 +2431,40 @@
         </is>
       </c>
       <c r="B46" t="n">
-        <v>397</v>
+        <v>289</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Bush Baked Beans</t>
+          <t>Little Yellows</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>5</v>
+        <v>4.99</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Groceries</t>
-        </is>
-      </c>
-      <c r="F46" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="G46" t="inlineStr">
-        <is>
-          <t>Bush Baked Beans | $5.00</t>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="F46" t="n">
+        <v>0</v>
+      </c>
+      <c r="G46" t="n">
+        <v>0</v>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>Groceries</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>Little Yellows | $4.99</t>
         </is>
       </c>
     </row>
@@ -1974,29 +2475,40 @@
         </is>
       </c>
       <c r="B47" t="n">
-        <v>411</v>
+        <v>293</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Baked Beans</t>
+          <t>Carrots</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>5</v>
+        <v>4.99</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Groceries</t>
-        </is>
-      </c>
-      <c r="F47" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="G47" t="inlineStr">
-        <is>
-          <t>Baked Beans | 2/ $5.00</t>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="F47" t="n">
+        <v>0</v>
+      </c>
+      <c r="G47" t="n">
+        <v>0</v>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>Groceries</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>C | $4.99</t>
         </is>
       </c>
     </row>
@@ -2007,29 +2519,40 @@
         </is>
       </c>
       <c r="B48" t="n">
-        <v>523</v>
+        <v>299</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>rere @</t>
+          <t>Onions Green</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>8.800000000000001</v>
+        <v>3.58</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Groceries</t>
-        </is>
-      </c>
-      <c r="F48" t="inlineStr">
+          <t>C</t>
+        </is>
+      </c>
+      <c r="F48" t="n">
+        <v>0</v>
+      </c>
+      <c r="G48" t="n">
+        <v>0</v>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>Groceries</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
         <is>
           <t>default</t>
         </is>
       </c>
-      <c r="G48" t="inlineStr">
-        <is>
-          <t>1.275 kg @ $8.80</t>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>Cnions Green | $3.58</t>
         </is>
       </c>
     </row>
@@ -2040,11 +2563,11 @@
         </is>
       </c>
       <c r="B49" t="n">
-        <v>579</v>
+        <v>309</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>2 oe l/</t>
+          <t>Cabbage Green</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2052,17 +2575,28 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Groceries</t>
-        </is>
-      </c>
-      <c r="F49" t="inlineStr">
+          <t>C</t>
+        </is>
+      </c>
+      <c r="F49" t="n">
+        <v>0</v>
+      </c>
+      <c r="G49" t="n">
+        <v>0</v>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>Groceries</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
         <is>
           <t>default</t>
         </is>
       </c>
-      <c r="G49" t="inlineStr">
-        <is>
-          <t>2 oe l/ | $3.28</t>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>Cabbage Green | $3.28</t>
         </is>
       </c>
     </row>
@@ -2073,29 +2607,40 @@
         </is>
       </c>
       <c r="B50" t="n">
-        <v>603</v>
+        <v>323</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Onions Red</t>
+          <t>Bananas</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>2.3</v>
+        <v>2.42</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Groceries</t>
-        </is>
-      </c>
-      <c r="F50" t="inlineStr">
-        <is>
-          <t>default</t>
-        </is>
-      </c>
-      <c r="G50" t="inlineStr">
-        <is>
-          <t>Onions Red | $2.30</t>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="F50" t="n">
+        <v>0</v>
+      </c>
+      <c r="G50" t="n">
+        <v>0</v>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>Groceries</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>Bananas | $2.42</t>
         </is>
       </c>
     </row>
@@ -2106,29 +2651,40 @@
         </is>
       </c>
       <c r="B51" t="n">
-        <v>611</v>
+        <v>331</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Smokies Orig Recipe</t>
+          <t>Onions Red</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>17.99</v>
+        <v>2.3</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Groceries</t>
-        </is>
-      </c>
-      <c r="F51" t="inlineStr">
+          <t>C</t>
+        </is>
+      </c>
+      <c r="F51" t="n">
+        <v>0</v>
+      </c>
+      <c r="G51" t="n">
+        <v>0</v>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>Groceries</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
         <is>
           <t>default</t>
         </is>
       </c>
-      <c r="G51" t="inlineStr">
-        <is>
-          <t>Smokies Orig Recipe | $17.99</t>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>oniahe ae | $2.30</t>
         </is>
       </c>
     </row>
@@ -2139,29 +2695,40 @@
         </is>
       </c>
       <c r="B52" t="n">
-        <v>615</v>
+        <v>611</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Hotdog All Beef</t>
+          <t>Smokies Orig Recipe</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>12.49</v>
+        <v>17.99</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Groceries</t>
-        </is>
-      </c>
-      <c r="F52" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="G52" t="inlineStr">
-        <is>
-          <t>Hotdog All Beef | $12.49</t>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="F52" t="n">
+        <v>0</v>
+      </c>
+      <c r="G52" t="n">
+        <v>0</v>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>Groceries</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>Smokies Orig Recipe | $17.99</t>
         </is>
       </c>
     </row>
@@ -2172,29 +2739,40 @@
         </is>
       </c>
       <c r="B53" t="n">
-        <v>619</v>
+        <v>615</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Chicken Wieners</t>
+          <t>Hotdog All Beef</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>3.79</v>
+        <v>12.49</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Groceries</t>
-        </is>
-      </c>
-      <c r="F53" t="inlineStr">
+          <t>C</t>
+        </is>
+      </c>
+      <c r="F53" t="n">
+        <v>0</v>
+      </c>
+      <c r="G53" t="n">
+        <v>0</v>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>Groceries</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
         <is>
           <t>exact</t>
         </is>
       </c>
-      <c r="G53" t="inlineStr">
-        <is>
-          <t>Chicken Wieners | $3.79</t>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>Hotdog All Beef | $12.49</t>
         </is>
       </c>
     </row>
@@ -2205,29 +2783,40 @@
         </is>
       </c>
       <c r="B54" t="n">
-        <v>625</v>
+        <v>619</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Cheese Slice Med Chd</t>
+          <t>Chicken Wieners</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>15.49</v>
+        <v>3.79</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Groceries</t>
-        </is>
-      </c>
-      <c r="F54" t="inlineStr">
+          <t>C</t>
+        </is>
+      </c>
+      <c r="F54" t="n">
+        <v>0</v>
+      </c>
+      <c r="G54" t="n">
+        <v>0</v>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>Groceries</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
         <is>
           <t>exact</t>
         </is>
       </c>
-      <c r="G54" t="inlineStr">
-        <is>
-          <t>Cheese Slice Med Chd | $15.49</t>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>Chicken Wieners | $3.79</t>
         </is>
       </c>
     </row>
@@ -2238,11 +2827,11 @@
         </is>
       </c>
       <c r="B55" t="n">
-        <v>635</v>
+        <v>623</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Ferogies Potato&amp;Ched</t>
+          <t>Cheese Slide Med Chd</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2250,17 +2839,28 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Groceries</t>
-        </is>
-      </c>
-      <c r="F55" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="G55" t="inlineStr">
-        <is>
-          <t>Marble Cheddar | $14.49</t>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="F55" t="n">
+        <v>0</v>
+      </c>
+      <c r="G55" t="n">
+        <v>0</v>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>Groceries</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>DE | $15.49 | INSTANT SAVINGS -1.00</t>
         </is>
       </c>
     </row>
@@ -2271,29 +2871,40 @@
         </is>
       </c>
       <c r="B56" t="n">
-        <v>643</v>
+        <v>635</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Chekn Brst Roast Ckd</t>
+          <t>Marble Cheddar</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>5.46</v>
+        <v>14.49</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Groceries</t>
-        </is>
-      </c>
-      <c r="F56" t="inlineStr">
+          <t>C</t>
+        </is>
+      </c>
+      <c r="F56" t="n">
+        <v>0</v>
+      </c>
+      <c r="G56" t="n">
+        <v>0</v>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>Groceries</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
         <is>
           <t>default</t>
         </is>
       </c>
-      <c r="G56" t="inlineStr">
-        <is>
-          <t>Chekn Brst Roast Ckd | $5.46</t>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>Marble Cheddar | $14.49</t>
         </is>
       </c>
     </row>
@@ -2304,29 +2915,40 @@
         </is>
       </c>
       <c r="B57" t="n">
-        <v>651</v>
+        <v>639</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Salami</t>
+          <t>Cheese Feta Light</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>4.17</v>
+        <v>6.99</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Groceries</t>
-        </is>
-      </c>
-      <c r="F57" t="inlineStr">
-        <is>
-          <t>default</t>
-        </is>
-      </c>
-      <c r="G57" t="inlineStr">
-        <is>
-          <t>Salami | $4.17</t>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="F57" t="n">
+        <v>0</v>
+      </c>
+      <c r="G57" t="n">
+        <v>0</v>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>Groceries</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>Cheese Feta Light | $6.99</t>
         </is>
       </c>
     </row>
@@ -2337,29 +2959,40 @@
         </is>
       </c>
       <c r="B58" t="n">
-        <v>655</v>
+        <v>643</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Ferogies Potato&amp;Ched</t>
+          <t>Chckn Brst Roast Ckd</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>14.49</v>
+        <v>5.46</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Groceries</t>
-        </is>
-      </c>
-      <c r="F58" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="G58" t="inlineStr">
-        <is>
-          <t>Ferogies Potato&amp;Ched | $14.49</t>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="F58" t="n">
+        <v>0</v>
+      </c>
+      <c r="G58" t="n">
+        <v>0</v>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>Groceries</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>Chekn Brst Roast Ckd | $5.46</t>
         </is>
       </c>
     </row>
@@ -2370,29 +3003,40 @@
         </is>
       </c>
       <c r="B59" t="n">
-        <v>659</v>
+        <v>651</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Perogies Potato&amp;Ched</t>
+          <t>Salami</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>7.49</v>
+        <v>4.17</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Groceries</t>
-        </is>
-      </c>
-      <c r="F59" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="G59" t="inlineStr">
-        <is>
-          <t>Perogies Potato&amp;Ched | $7.49</t>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="F59" t="n">
+        <v>0</v>
+      </c>
+      <c r="G59" t="n">
+        <v>0</v>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>Groceries</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>Salami | $4.17</t>
         </is>
       </c>
     </row>
@@ -2403,29 +3047,40 @@
         </is>
       </c>
       <c r="B60" t="n">
-        <v>665</v>
+        <v>655</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Garlic Spread</t>
+          <t>Perogies Potato&amp;Ched</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>4.72</v>
+        <v>14.49</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Groceries</t>
-        </is>
-      </c>
-      <c r="F60" t="inlineStr">
-        <is>
-          <t>default</t>
-        </is>
-      </c>
-      <c r="G60" t="inlineStr">
-        <is>
-          <t>Garlic Spread | $4.72</t>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="F60" t="n">
+        <v>0</v>
+      </c>
+      <c r="G60" t="n">
+        <v>0</v>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>Groceries</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>Ferogies Potato&amp;Ched | $14.49</t>
         </is>
       </c>
     </row>
@@ -2436,29 +3091,40 @@
         </is>
       </c>
       <c r="B61" t="n">
-        <v>669</v>
+        <v>659</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Baguette White</t>
+          <t>Perogies Potato&amp;Ched</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>3.99</v>
+        <v>7.49</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Groceries</t>
-        </is>
-      </c>
-      <c r="F61" t="inlineStr">
-        <is>
-          <t>ai_cache</t>
-        </is>
-      </c>
-      <c r="G61" t="inlineStr">
-        <is>
-          <t>Baguette White | $3.99</t>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="F61" t="n">
+        <v>0</v>
+      </c>
+      <c r="G61" t="n">
+        <v>0</v>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>Groceries</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>Perogies Potato&amp;Ched | $7.49</t>
         </is>
       </c>
     </row>
@@ -2469,29 +3135,216 @@
         </is>
       </c>
       <c r="B62" t="n">
-        <v>691</v>
+        <v>665</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>ee a</t>
+          <t>Garlic Spread</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>3.37</v>
+        <v>4.72</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Groceries</t>
-        </is>
-      </c>
-      <c r="F62" t="inlineStr">
+          <t>C</t>
+        </is>
+      </c>
+      <c r="F62" t="n">
+        <v>0</v>
+      </c>
+      <c r="G62" t="n">
+        <v>0</v>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>Groceries</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
         <is>
           <t>default</t>
         </is>
       </c>
-      <c r="G62" t="inlineStr">
-        <is>
-          <t>ee a | $3.37</t>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>Garlic Spread | $4.72</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>20260214_sobeys_363_95</t>
+        </is>
+      </c>
+      <c r="B63" t="n">
+        <v>669</v>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Baguette White</t>
+        </is>
+      </c>
+      <c r="D63" t="n">
+        <v>3.99</v>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="F63" t="n">
+        <v>0</v>
+      </c>
+      <c r="G63" t="n">
+        <v>0</v>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>Groceries</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>ai_cache</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>Baguette White | $3.99</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>20260214_sobeys_363_95</t>
+        </is>
+      </c>
+      <c r="B64" t="n">
+        <v>673</v>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Sausage Buns</t>
+        </is>
+      </c>
+      <c r="D64" t="n">
+        <v>5.49</v>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="F64" t="n">
+        <v>0</v>
+      </c>
+      <c r="G64" t="n">
+        <v>0</v>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>Groceries</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>Sausage Buns | $5.49</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>20260214_sobeys_363_95</t>
+        </is>
+      </c>
+      <c r="B65" t="n">
+        <v>677</v>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Buns Hot Dog</t>
+        </is>
+      </c>
+      <c r="D65" t="n">
+        <v>4.99</v>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="F65" t="n">
+        <v>0</v>
+      </c>
+      <c r="G65" t="n">
+        <v>0</v>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>Groceries</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>Buns Hot Dog | $4.99</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>20260214_sobeys_363_95</t>
+        </is>
+      </c>
+      <c r="B66" t="n">
+        <v>681</v>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>English Muffins Sour</t>
+        </is>
+      </c>
+      <c r="D66" t="n">
+        <v>3.49</v>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="F66" t="n">
+        <v>0</v>
+      </c>
+      <c r="G66" t="n">
+        <v>0</v>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>Groceries</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>English Muffins Sour | $3.49</t>
         </is>
       </c>
     </row>
@@ -2584,7 +3437,7 @@
         <v>363.95</v>
       </c>
       <c r="H2" t="n">
-        <v>61</v>
+        <v>71</v>
       </c>
     </row>
   </sheetData>
@@ -3239,7 +4092,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="60" customWidth="1" min="1" max="1"/>
@@ -3255,28 +4108,35 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Input path: /Users/paul/Developer/home-budget-pipeline/receipts/Sobeys</t>
+          <t>Imported manual workbook: /Users/paul/Developer/home-budget-pipeline/sobeys_one.xlsx</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Receipts parsed: 1</t>
+          <t>Input path: /Users/paul/Developer/home-budget-pipeline/receipts/Sobeys</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Items parsed: 61</t>
+          <t>Receipts parsed: 1</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>AI Status: enabled=True, disabled_runtime=False, calls=0, batch_items=0, ai_cache_hits=1, success=0, api_errors=0.</t>
+          <t>Items parsed: 65</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>AI Status: enabled=True, disabled_runtime=False, calls=0, batch_items=0, ai_cache_hits=0, success=0, api_errors=0.</t>
         </is>
       </c>
     </row>

--- a/sobeys_receipt_items_categorized.xlsx
+++ b/sobeys_receipt_items_categorized.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J66"/>
+  <dimension ref="A1:J62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -441,11 +441,11 @@
     <col width="23" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
     <col width="6" customWidth="1" min="5" max="5"/>
-    <col width="21" customWidth="1" min="6" max="6"/>
-    <col width="21" customWidth="1" min="7" max="7"/>
+    <col width="5" customWidth="1" min="6" max="6"/>
+    <col width="5" customWidth="1" min="7" max="7"/>
     <col width="17" customWidth="1" min="8" max="8"/>
     <col width="17" customWidth="1" min="9" max="9"/>
-    <col width="53" customWidth="1" min="10" max="10"/>
+    <col width="34" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -507,26 +507,15 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Comp Quick Oats 1KG</t>
+          <t>Pie Filling S/Berry</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>4.79</v>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="F2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G2" t="n">
-        <v>0</v>
+        <v>6.49</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -535,10 +524,14 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>default</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr"/>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>Gep Pic Med | $6.49</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -547,26 +540,15 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Vinta Crackers</t>
+          <t>Pie Filling S/Berry</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>4.29</v>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="F3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G3" t="n">
-        <v>0</v>
+        <v>6.49</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -578,7 +560,11 @@
           <t>exact</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr"/>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Cep Pic Med | $6.49</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -587,26 +573,15 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Candy GMS Org</t>
+          <t>Pie Filling S/Berry</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>3.49</v>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>BC</t>
-        </is>
-      </c>
-      <c r="F4" t="n">
-        <v>0.1745</v>
-      </c>
-      <c r="G4" t="n">
-        <v>0.2443</v>
+        <v>6.49</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -618,7 +593,11 @@
           <t>exact</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr"/>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Pie Filling S/Berry | $6.49</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -627,27 +606,16 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3</v>
+        <v>23</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Oep Pic Med</t>
+          <t>Pie Filling S/Berry</t>
         </is>
       </c>
       <c r="D5" t="n">
         <v>6.49</v>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="F5" t="n">
-        <v>0</v>
-      </c>
-      <c r="G5" t="n">
-        <v>0</v>
-      </c>
       <c r="H5" t="inlineStr">
         <is>
           <t>Groceries</t>
@@ -655,12 +623,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>default</t>
+          <t>exact</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>GROCERY | $6.49</t>
+          <t>Pie Filling S/Berry | $6.49</t>
         </is>
       </c>
     </row>
@@ -671,26 +639,15 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>9</v>
+        <v>31</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Oep Pic Med</t>
+          <t>Pretzels HoneyMustar</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>5.99</v>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="F6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G6" t="n">
-        <v>0</v>
+        <v>5.49</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -704,7 +661,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Cep Pic Med | $6.49 | INSTANT SAVINGS -0.50</t>
+          <t>200 PTS | $5.49 BC</t>
         </is>
       </c>
     </row>
@@ -715,26 +672,15 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>13</v>
+        <v>37</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Pie Filling S/Berry</t>
+          <t>Pretzels HoneyMustar</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>5.99</v>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="F7" t="n">
-        <v>0</v>
-      </c>
-      <c r="G7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
@@ -743,12 +689,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>exact</t>
+          <t>default</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Pie Filling S/Berry | $6.49 | INSTANT SAVINGS -0.50</t>
+          <t>Pretzels HoneyMustar | $1.00 |</t>
         </is>
       </c>
     </row>
@@ -759,26 +705,15 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>23</v>
+        <v>43</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Pie Filling S/Berry</t>
+          <t>Pretzel Cracker Rahe</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>6.49</v>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="F8" t="n">
-        <v>0</v>
-      </c>
-      <c r="G8" t="n">
-        <v>0</v>
+        <v>5.49</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -792,7 +727,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Pie Filling S/Berry | $6.49</t>
+          <t>Pretzel Cracker Rahe | $5.49 BC</t>
         </is>
       </c>
     </row>
@@ -803,26 +738,15 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>37</v>
+        <v>51</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Pretzels HoneyMustar</t>
+          <t>Chips Rstrnt Sty Lin</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>5.49</v>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>BC</t>
-        </is>
-      </c>
-      <c r="F9" t="n">
-        <v>0.2745</v>
-      </c>
-      <c r="G9" t="n">
-        <v>0.3843</v>
+        <v>5.29</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
@@ -831,12 +755,12 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>default</t>
+          <t>exact</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Pretzels HoneyMustar | $1.00 |</t>
+          <t>Chips Multigrai | $5.29 BC</t>
         </is>
       </c>
     </row>
@@ -847,26 +771,15 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>43</v>
+        <v>69</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Pretzel Cracker Rach</t>
+          <t>Comp Quick Oats 1KG</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>5.49</v>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>BC</t>
-        </is>
-      </c>
-      <c r="F10" t="n">
-        <v>0.2745</v>
-      </c>
-      <c r="G10" t="n">
-        <v>0.3843</v>
+        <v>4.79</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
@@ -875,12 +788,12 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>exact</t>
+          <t>default</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Pretzel Cracker Rahe | $5.49 BC</t>
+          <t>YOU SAV | $4.79</t>
         </is>
       </c>
     </row>
@@ -891,30 +804,19 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>51</v>
+        <v>81</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Chips Multigrain</t>
+          <t>Gloves Cmfrt Med 1EA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>5.29</v>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>BC</t>
-        </is>
-      </c>
-      <c r="F11" t="n">
-        <v>0.2645</v>
-      </c>
-      <c r="G11" t="n">
-        <v>0.3703</v>
+        <v>4.29</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Groceries</t>
+          <t>Clothing</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -924,7 +826,7 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>Chips Multigrai | $5.29 BC</t>
+          <t>Vinta Crackers | $4.29</t>
         </is>
       </c>
     </row>
@@ -935,26 +837,15 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Chips Rstrnt Sty Lm</t>
+          <t>Pepsi Zero</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>5.29</v>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>BC</t>
-        </is>
-      </c>
-      <c r="F12" t="n">
-        <v>0.2645</v>
-      </c>
-      <c r="G12" t="n">
-        <v>0.3703</v>
+        <v>4.25</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
@@ -968,7 +859,7 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>C | $4.29</t>
+          <t>Pepsi Zero | $4.25</t>
         </is>
       </c>
     </row>
@@ -979,26 +870,15 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>85</v>
+        <v>97</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Dil Pkls Xt Grlc Snd</t>
+          <t>Pepsi Zero</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>4.99</v>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="F13" t="n">
-        <v>0</v>
-      </c>
-      <c r="G13" t="n">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
@@ -1012,7 +892,7 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>BC | $4.25</t>
+          <t>Pepsi Zero | $4.25 BC</t>
         </is>
       </c>
     </row>
@@ -1023,26 +903,15 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>97</v>
+        <v>109</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Pepsi Zero</t>
+          <t>English Muffins Sour</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>4.37</v>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>BC</t>
-        </is>
-      </c>
-      <c r="F14" t="n">
-        <v>0.2125</v>
-      </c>
-      <c r="G14" t="n">
-        <v>0.2975</v>
+        <v>3.49</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
@@ -1051,12 +920,12 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>default</t>
+          <t>exact</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>Pepsi Zero | $4.25 BC | EHC 0.12</t>
+          <t>Candy GMS Org | $3.49 BC</t>
         </is>
       </c>
     </row>
@@ -1067,26 +936,15 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>97</v>
+        <v>115</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Pepsi Zero</t>
+          <t>English Muffins Sour</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>4.37</v>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>BC</t>
-        </is>
-      </c>
-      <c r="F15" t="n">
-        <v>0.2125</v>
-      </c>
-      <c r="G15" t="n">
-        <v>0.2975</v>
+        <v>3.49</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
@@ -1095,12 +953,12 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>default</t>
+          <t>exact</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>Pepsi Zero | $4.25 BC | EHC 0.12</t>
+          <t>Candy GMS Ors | $3.49 BC</t>
         </is>
       </c>
     </row>
@@ -1111,26 +969,15 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>107</v>
+        <v>123</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Mexican Hot Sauce</t>
+          <t>English Muffins Sour</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>3.69</v>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="F16" t="n">
-        <v>0</v>
-      </c>
-      <c r="G16" t="n">
-        <v>0</v>
+        <v>3.49</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
@@ -1144,7 +991,7 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>Mexican Hot Sauce | $3.49 BC</t>
+          <t>Candy GMS Or¢ | $3.49 BC</t>
         </is>
       </c>
     </row>
@@ -1155,26 +1002,15 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>115</v>
+        <v>131</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Candy GMS Org</t>
+          <t>Lindor 3Pk</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>3.49</v>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>BC</t>
-        </is>
-      </c>
-      <c r="F17" t="n">
-        <v>0.1745</v>
-      </c>
-      <c r="G17" t="n">
-        <v>0.2443</v>
+        <v>2.99</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
@@ -1183,12 +1019,12 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>exact</t>
+          <t>default</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>Candy GMS Ors | $3.49 BC</t>
+          <t>Lindor 3Pk | $2.99 BC</t>
         </is>
       </c>
     </row>
@@ -1199,26 +1035,15 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>123</v>
+        <v>135</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Candy GMS Org</t>
+          <t>Lindor 3Pk</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>3.49</v>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>BC</t>
-        </is>
-      </c>
-      <c r="F18" t="n">
-        <v>0.1745</v>
-      </c>
-      <c r="G18" t="n">
-        <v>0.2443</v>
+        <v>2.99</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
@@ -1227,12 +1052,12 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>exact</t>
+          <t>default</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>Candy GMS Or¢ | $3.49 BC</t>
+          <t>Lindor 3Pk | $2.99 BC</t>
         </is>
       </c>
     </row>
@@ -1243,7 +1068,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>131</v>
+        <v>139</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -1253,17 +1078,6 @@
       <c r="D19" t="n">
         <v>2.99</v>
       </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>BC</t>
-        </is>
-      </c>
-      <c r="F19" t="n">
-        <v>0.1495</v>
-      </c>
-      <c r="G19" t="n">
-        <v>0.2093</v>
-      </c>
       <c r="H19" t="inlineStr">
         <is>
           <t>Groceries</t>
@@ -1276,7 +1090,7 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>Lindor 3Pk | $2.99 BC</t>
+          <t>Lindor 3Pk | $2.99 ps</t>
         </is>
       </c>
     </row>
@@ -1287,26 +1101,15 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>135</v>
+        <v>143</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Lindor 3Pk</t>
+          <t>Chicken Broth</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>2.99</v>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>BC</t>
-        </is>
-      </c>
-      <c r="F20" t="n">
-        <v>0.1495</v>
-      </c>
-      <c r="G20" t="n">
-        <v>0.2093</v>
+        <v>2.89</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
@@ -1315,12 +1118,12 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>default</t>
+          <t>exact</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>Lindor 3Pk | $2.99 BC</t>
+          <t>Chicken Broth | $2.89</t>
         </is>
       </c>
     </row>
@@ -1331,26 +1134,15 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>139</v>
+        <v>147</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Lindor 3Pk</t>
+          <t>Bush Baked Beans</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>2.99</v>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>BC</t>
-        </is>
-      </c>
-      <c r="F21" t="n">
-        <v>0.1495</v>
-      </c>
-      <c r="G21" t="n">
-        <v>0.2093</v>
+        <v>2.5</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
@@ -1359,12 +1151,12 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>default</t>
+          <t>exact</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>Lindor 3Pk | $2.99 ps</t>
+          <t>Bush Baked Beans | $2.50</t>
         </is>
       </c>
     </row>
@@ -1375,26 +1167,15 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>143</v>
+        <v>157</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Chicken Broth</t>
+          <t>Bush Baked Beans</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>2.89</v>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="F22" t="n">
-        <v>0</v>
-      </c>
-      <c r="G22" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
@@ -1408,7 +1189,7 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>Chicken Broth | $2.89</t>
+          <t>Baked Beans | $2.50</t>
         </is>
       </c>
     </row>
@@ -1419,26 +1200,15 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>147</v>
+        <v>167</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Bush Baked Beans</t>
+          <t>Cake Mx CarrotSprmst</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="F23" t="n">
-        <v>0</v>
-      </c>
-      <c r="G23" t="n">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
@@ -1447,12 +1217,12 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>exact</t>
+          <t>default</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>Bush Baked Beans | $2.50</t>
+          <t>Green Relish | $2.49</t>
         </is>
       </c>
     </row>
@@ -1463,26 +1233,15 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>157</v>
+        <v>175</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Baked Beans</t>
+          <t>Cake Mx CarrotSprmst</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="F24" t="n">
-        <v>0</v>
-      </c>
-      <c r="G24" t="n">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
@@ -1491,12 +1250,12 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>exact</t>
+          <t>default</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>Baked Beans | $2.50</t>
+          <t>Cake Mx CarrotSprimst | $2.49</t>
         </is>
       </c>
     </row>
@@ -1507,27 +1266,16 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>167</v>
+        <v>185</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Green Relish</t>
+          <t>Cake Mix French Van</t>
         </is>
       </c>
       <c r="D25" t="n">
         <v>2.49</v>
       </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="F25" t="n">
-        <v>0</v>
-      </c>
-      <c r="G25" t="n">
-        <v>0</v>
-      </c>
       <c r="H25" t="inlineStr">
         <is>
           <t>Groceries</t>
@@ -1540,7 +1288,7 @@
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>Green Relish | $2.49</t>
+          <t>Cake Mix French Van | $2.49</t>
         </is>
       </c>
     </row>
@@ -1551,26 +1299,15 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>175</v>
+        <v>193</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Cake Mx CarrotSprmst</t>
+          <t>Licorice S/Berry</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>2.49</v>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="F26" t="n">
-        <v>0</v>
-      </c>
-      <c r="G26" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
@@ -1579,12 +1316,12 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>default</t>
+          <t>exact</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>Cake Mx CarrotSprimst | $2.49</t>
+          <t>Licorice $/Berry | $1.79 BC</t>
         </is>
       </c>
     </row>
@@ -1595,26 +1332,15 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>185</v>
+        <v>197</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Cake Mix French Van</t>
+          <t>Licorice S/Berry</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>2.49</v>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="F27" t="n">
-        <v>0</v>
-      </c>
-      <c r="G27" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>
@@ -1623,12 +1349,12 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>default</t>
+          <t>exact</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>Cake Mix French Van | $2.49</t>
+          <t>Licorice S/Berry | $1.79 BC</t>
         </is>
       </c>
     </row>
@@ -1639,7 +1365,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>193</v>
+        <v>201</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -1649,17 +1375,6 @@
       <c r="D28" t="n">
         <v>1.79</v>
       </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>BC</t>
-        </is>
-      </c>
-      <c r="F28" t="n">
-        <v>0.08950000000000001</v>
-      </c>
-      <c r="G28" t="n">
-        <v>0.1253</v>
-      </c>
       <c r="H28" t="inlineStr">
         <is>
           <t>Groceries</t>
@@ -1672,7 +1387,7 @@
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>Licorice $/Berry | $1.79 BC</t>
+          <t>Licorice S/Berry | $1.79 BC</t>
         </is>
       </c>
     </row>
@@ -1683,30 +1398,19 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>197</v>
+        <v>205</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Licorice S/Berry</t>
+          <t>Gloves Cmfrt Med 1EA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>BC</t>
-        </is>
-      </c>
-      <c r="F29" t="n">
-        <v>0.08950000000000001</v>
-      </c>
-      <c r="G29" t="n">
-        <v>0.1253</v>
+        <v>4.29</v>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Groceries</t>
+          <t>Clothing</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -1716,7 +1420,7 @@
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>Licorice S/Berry | $1.79 BC</t>
+          <t>Gloves Cmfrt Med 1EA | $4.29 BC</t>
         </is>
       </c>
     </row>
@@ -1727,30 +1431,19 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>201</v>
+        <v>209</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Licorice S/Berry</t>
+          <t>Gloves Cmnfrt Med 1EA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>BC</t>
-        </is>
-      </c>
-      <c r="F30" t="n">
-        <v>0.08950000000000001</v>
-      </c>
-      <c r="G30" t="n">
-        <v>0.1253</v>
+        <v>4.29</v>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Groceries</t>
+          <t>Clothing</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -1760,7 +1453,7 @@
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>Licorice S/Berry | $1.79 BC</t>
+          <t>Gloves Cmnfrt Med 1EA | $4.29 BC</t>
         </is>
       </c>
     </row>
@@ -1771,30 +1464,19 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>205</v>
+        <v>213</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Gloves Cmfrt Med 1EA</t>
+          <t>“Mexican Hot Sauce</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>4.29</v>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>BC</t>
-        </is>
-      </c>
-      <c r="F31" t="n">
-        <v>0.2145</v>
-      </c>
-      <c r="G31" t="n">
-        <v>0.3003</v>
+        <v>3.69</v>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Clothing</t>
+          <t>Groceries</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -1804,7 +1486,7 @@
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>Gloves Cmfrt Med 1EA | $4.29 BC</t>
+          <t>Scourer Refill] 1EA | $3.69 BC</t>
         </is>
       </c>
     </row>
@@ -1815,30 +1497,19 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>209</v>
+        <v>217</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Gloves Cmnfrt Med 1EA</t>
+          <t>Butter Sticks Unsltd</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>4.29</v>
-      </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>BC</t>
-        </is>
-      </c>
-      <c r="F32" t="n">
-        <v>0.2145</v>
-      </c>
-      <c r="G32" t="n">
-        <v>0.3003</v>
+        <v>8.49</v>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Clothing</t>
+          <t>Groceries</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -1848,7 +1519,7 @@
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>Gloves Cmnfrt Med 1EA | $4.29 BC</t>
+          <t>Butter Sticks Unsltd | $8.49</t>
         </is>
       </c>
     </row>
@@ -1859,26 +1530,15 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>213</v>
+        <v>227</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Scourer Refill 1EA</t>
+          <t>Sour Cream Light</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>3.69</v>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>BC</t>
-        </is>
-      </c>
-      <c r="F33" t="n">
-        <v>0.1845</v>
-      </c>
-      <c r="G33" t="n">
-        <v>0.2583</v>
+        <v>4.89</v>
       </c>
       <c r="H33" t="inlineStr">
         <is>
@@ -1887,12 +1547,12 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>default</t>
+          <t>exact</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>Scourer Refill] 1EA | $3.69 BC</t>
+          <t>Sour Cream Light | $4.89</t>
         </is>
       </c>
     </row>
@@ -1903,30 +1563,19 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>217</v>
+        <v>235</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Butter Sticks Unsltd</t>
+          <t>Topping Dessert 1L</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>8.49</v>
-      </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="F34" t="n">
-        <v>0</v>
-      </c>
-      <c r="G34" t="n">
-        <v>0</v>
+        <v>5.99</v>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Groceries</t>
+          <t>Clothing</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -1936,7 +1585,7 @@
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>Butter Sticks Unsltd | $8.49</t>
+          <t>eon tr 2 uescort aE | $5.99</t>
         </is>
       </c>
     </row>
@@ -1947,26 +1596,15 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>223</v>
+        <v>241</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Cottage Cheese 1%MF</t>
+          <t>Apples Honeycrisp</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>6.49</v>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="F35" t="n">
-        <v>0</v>
-      </c>
-      <c r="G35" t="n">
-        <v>0</v>
+        <v>11.22</v>
       </c>
       <c r="H35" t="inlineStr">
         <is>
@@ -1980,7 +1618,7 @@
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>Cottage Cheese 1%MF | $6.49</t>
+          <t>piglet foeycr en | $11.22</t>
         </is>
       </c>
     </row>
@@ -1991,26 +1629,15 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>227</v>
+        <v>253</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Sour Cream Light</t>
+          <t>Mango Spears</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>4.89</v>
-      </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="F36" t="n">
-        <v>0</v>
-      </c>
-      <c r="G36" t="n">
-        <v>0</v>
+        <v>8.99</v>
       </c>
       <c r="H36" t="inlineStr">
         <is>
@@ -2019,12 +1646,12 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>exact</t>
+          <t>default</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>Sour Cream Light | $4.89</t>
+          <t>Mango ale | $8.99</t>
         </is>
       </c>
     </row>
@@ -2035,26 +1662,15 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>231</v>
+        <v>257</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Cottage Cheese 1%MF</t>
+          <t>Cheese Feta Light</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>4.79</v>
-      </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="F37" t="n">
-        <v>0</v>
-      </c>
-      <c r="G37" t="n">
-        <v>0</v>
+        <v>6.99</v>
       </c>
       <c r="H37" t="inlineStr">
         <is>
@@ -2068,7 +1684,7 @@
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>Cottage Cheese 1%MF | $4.79</t>
+          <t>Basil Freeze Drd 8G | $6.99</t>
         </is>
       </c>
     </row>
@@ -2079,26 +1695,15 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>235</v>
+        <v>261</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Topping Dessert 1L</t>
+          <t>Cheese Feta Light</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>5.99</v>
-      </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="F38" t="n">
-        <v>0</v>
-      </c>
-      <c r="G38" t="n">
-        <v>0</v>
+        <v>6.99</v>
       </c>
       <c r="H38" t="inlineStr">
         <is>
@@ -2107,12 +1712,12 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>default</t>
+          <t>exact</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>eon tr 2 uescort aE | $5.99</t>
+          <t>Dill Freeze Ord 10G | $6.99</t>
         </is>
       </c>
     </row>
@@ -2123,26 +1728,15 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>239</v>
+        <v>265</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Apples Honeycrisp</t>
+          <t>Pie Filling S/Berry</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>11.22</v>
-      </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="F39" t="n">
-        <v>0</v>
-      </c>
-      <c r="G39" t="n">
-        <v>0</v>
+        <v>6.49</v>
       </c>
       <c r="H39" t="inlineStr">
         <is>
@@ -2151,12 +1745,12 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>default</t>
+          <t>exact</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>PRO | $11.22</t>
+          <t>Asparagus | $6.49</t>
         </is>
       </c>
     </row>
@@ -2167,26 +1761,15 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>253</v>
+        <v>289</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Mango Spears</t>
+          <t>Dil Pkls Xt Grle Snd</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>8.99</v>
-      </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="F40" t="n">
-        <v>0</v>
-      </c>
-      <c r="G40" t="n">
-        <v>0</v>
+        <v>4.99</v>
       </c>
       <c r="H40" t="inlineStr">
         <is>
@@ -2200,7 +1783,7 @@
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>Mango ale | $8.99</t>
+          <t>Little Yellows | $4.99</t>
         </is>
       </c>
     </row>
@@ -2211,26 +1794,15 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>257</v>
+        <v>295</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Basil Freeze Drd 8G</t>
+          <t>Dil Pkls Xt Grle Snd</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>6.99</v>
-      </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="F41" t="n">
-        <v>0</v>
-      </c>
-      <c r="G41" t="n">
-        <v>0</v>
+        <v>4.99</v>
       </c>
       <c r="H41" t="inlineStr">
         <is>
@@ -2244,7 +1816,7 @@
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>Basil Freeze Drd 8G | $6.99</t>
+          <t>Carrots | $4.99</t>
         </is>
       </c>
     </row>
@@ -2255,26 +1827,15 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>261</v>
+        <v>299</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Dill Freeze Ord 10G</t>
+          <t>Onions Green</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>6.99</v>
-      </c>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="F42" t="n">
-        <v>0</v>
-      </c>
-      <c r="G42" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="H42" t="inlineStr">
         <is>
@@ -2288,7 +1849,7 @@
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>Dill Freeze Ord 10G | $6.99</t>
+          <t>Cnions Green | $3.58</t>
         </is>
       </c>
     </row>
@@ -2299,26 +1860,15 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>265</v>
+        <v>309</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Asparagus</t>
+          <t>Cabbage Green</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>6.49</v>
-      </c>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="F43" t="n">
-        <v>0</v>
-      </c>
-      <c r="G43" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="H43" t="inlineStr">
         <is>
@@ -2332,7 +1882,7 @@
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>Asparagus | $6.49</t>
+          <t>Cabbage Green | $3.28</t>
         </is>
       </c>
     </row>
@@ -2343,26 +1893,15 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>277</v>
+        <v>323</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Org Straws</t>
+          <t>Bananas</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>6.49</v>
-      </c>
-      <c r="E44" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="F44" t="n">
-        <v>0</v>
-      </c>
-      <c r="G44" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="H44" t="inlineStr">
         <is>
@@ -2376,7 +1915,7 @@
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>Org Straws | $6.49</t>
+          <t>Bananas | $2.42</t>
         </is>
       </c>
     </row>
@@ -2387,26 +1926,15 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>283</v>
+        <v>331</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Strawberries 1lb</t>
+          <t>oniahe ae</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>6.49</v>
-      </c>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="F45" t="n">
-        <v>0</v>
-      </c>
-      <c r="G45" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="H45" t="inlineStr">
         <is>
@@ -2415,12 +1943,12 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>exact</t>
+          <t>default</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>Strawberries 11b | $6.49</t>
+          <t>oniahe ae | $2.30</t>
         </is>
       </c>
     </row>
@@ -2431,26 +1959,15 @@
         </is>
       </c>
       <c r="B46" t="n">
-        <v>289</v>
+        <v>397</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Little Yellows</t>
+          <t>Bush Baked Beans</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>4.99</v>
-      </c>
-      <c r="E46" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="F46" t="n">
-        <v>0</v>
-      </c>
-      <c r="G46" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H46" t="inlineStr">
         <is>
@@ -2459,12 +1976,12 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>default</t>
+          <t>exact</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>Little Yellows | $4.99</t>
+          <t>Bush Baked Beans | $5.00</t>
         </is>
       </c>
     </row>
@@ -2475,26 +1992,15 @@
         </is>
       </c>
       <c r="B47" t="n">
-        <v>293</v>
+        <v>411</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Carrots</t>
+          <t>Baked Beans</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>4.99</v>
-      </c>
-      <c r="E47" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="F47" t="n">
-        <v>0</v>
-      </c>
-      <c r="G47" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H47" t="inlineStr">
         <is>
@@ -2503,12 +2009,12 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>default</t>
+          <t>exact</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>C | $4.99</t>
+          <t>Baked Beans | 2/ $5.00</t>
         </is>
       </c>
     </row>
@@ -2519,26 +2025,15 @@
         </is>
       </c>
       <c r="B48" t="n">
-        <v>299</v>
+        <v>523</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Onions Green</t>
+          <t>rere @</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>3.58</v>
-      </c>
-      <c r="E48" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="F48" t="n">
-        <v>0</v>
-      </c>
-      <c r="G48" t="n">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="H48" t="inlineStr">
         <is>
@@ -2552,7 +2047,7 @@
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>Cnions Green | $3.58</t>
+          <t>1.275 kg @ $8.80</t>
         </is>
       </c>
     </row>
@@ -2563,27 +2058,16 @@
         </is>
       </c>
       <c r="B49" t="n">
-        <v>309</v>
+        <v>579</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Cabbage Green</t>
+          <t>2 oe l/</t>
         </is>
       </c>
       <c r="D49" t="n">
         <v>3.28</v>
       </c>
-      <c r="E49" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="F49" t="n">
-        <v>0</v>
-      </c>
-      <c r="G49" t="n">
-        <v>0</v>
-      </c>
       <c r="H49" t="inlineStr">
         <is>
           <t>Groceries</t>
@@ -2596,7 +2080,7 @@
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>Cabbage Green | $3.28</t>
+          <t>2 oe l/ | $3.28</t>
         </is>
       </c>
     </row>
@@ -2607,26 +2091,15 @@
         </is>
       </c>
       <c r="B50" t="n">
-        <v>323</v>
+        <v>603</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Bananas</t>
+          <t>Onions Red</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>2.42</v>
-      </c>
-      <c r="E50" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="F50" t="n">
-        <v>0</v>
-      </c>
-      <c r="G50" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="H50" t="inlineStr">
         <is>
@@ -2635,12 +2108,12 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>exact</t>
+          <t>default</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>Bananas | $2.42</t>
+          <t>Onions Red | $2.30</t>
         </is>
       </c>
     </row>
@@ -2651,26 +2124,15 @@
         </is>
       </c>
       <c r="B51" t="n">
-        <v>331</v>
+        <v>611</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Onions Red</t>
+          <t>Smokies Orig Recipe</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="E51" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="F51" t="n">
-        <v>0</v>
-      </c>
-      <c r="G51" t="n">
-        <v>0</v>
+        <v>17.99</v>
       </c>
       <c r="H51" t="inlineStr">
         <is>
@@ -2684,7 +2146,7 @@
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>oniahe ae | $2.30</t>
+          <t>Smokies Orig Recipe | $17.99</t>
         </is>
       </c>
     </row>
@@ -2695,26 +2157,15 @@
         </is>
       </c>
       <c r="B52" t="n">
-        <v>611</v>
+        <v>615</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Smokies Orig Recipe</t>
+          <t>Hotdog All Beef</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>17.99</v>
-      </c>
-      <c r="E52" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="F52" t="n">
-        <v>0</v>
-      </c>
-      <c r="G52" t="n">
-        <v>0</v>
+        <v>12.49</v>
       </c>
       <c r="H52" t="inlineStr">
         <is>
@@ -2723,12 +2174,12 @@
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>default</t>
+          <t>exact</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>Smokies Orig Recipe | $17.99</t>
+          <t>Hotdog All Beef | $12.49</t>
         </is>
       </c>
     </row>
@@ -2739,26 +2190,15 @@
         </is>
       </c>
       <c r="B53" t="n">
-        <v>615</v>
+        <v>619</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Hotdog All Beef</t>
+          <t>Chicken Wieners</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>12.49</v>
-      </c>
-      <c r="E53" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="F53" t="n">
-        <v>0</v>
-      </c>
-      <c r="G53" t="n">
-        <v>0</v>
+        <v>3.79</v>
       </c>
       <c r="H53" t="inlineStr">
         <is>
@@ -2772,7 +2212,7 @@
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>Hotdog All Beef | $12.49</t>
+          <t>Chicken Wieners | $3.79</t>
         </is>
       </c>
     </row>
@@ -2783,26 +2223,15 @@
         </is>
       </c>
       <c r="B54" t="n">
-        <v>619</v>
+        <v>625</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Chicken Wieners</t>
+          <t>Cheese Slice Med Chd</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>3.79</v>
-      </c>
-      <c r="E54" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="F54" t="n">
-        <v>0</v>
-      </c>
-      <c r="G54" t="n">
-        <v>0</v>
+        <v>15.49</v>
       </c>
       <c r="H54" t="inlineStr">
         <is>
@@ -2816,7 +2245,7 @@
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>Chicken Wieners | $3.79</t>
+          <t>Cheese Slice Med Chd | $15.49</t>
         </is>
       </c>
     </row>
@@ -2827,27 +2256,16 @@
         </is>
       </c>
       <c r="B55" t="n">
-        <v>623</v>
+        <v>635</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Cheese Slide Med Chd</t>
+          <t>Ferogies Potato&amp;Ched</t>
         </is>
       </c>
       <c r="D55" t="n">
         <v>14.49</v>
       </c>
-      <c r="E55" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="F55" t="n">
-        <v>0</v>
-      </c>
-      <c r="G55" t="n">
-        <v>0</v>
-      </c>
       <c r="H55" t="inlineStr">
         <is>
           <t>Groceries</t>
@@ -2855,12 +2273,12 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>default</t>
+          <t>exact</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>DE | $15.49 | INSTANT SAVINGS -1.00</t>
+          <t>Marble Cheddar | $14.49</t>
         </is>
       </c>
     </row>
@@ -2871,26 +2289,15 @@
         </is>
       </c>
       <c r="B56" t="n">
-        <v>635</v>
+        <v>643</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Marble Cheddar</t>
+          <t>Chekn Brst Roast Ckd</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>14.49</v>
-      </c>
-      <c r="E56" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="F56" t="n">
-        <v>0</v>
-      </c>
-      <c r="G56" t="n">
-        <v>0</v>
+        <v>5.46</v>
       </c>
       <c r="H56" t="inlineStr">
         <is>
@@ -2904,7 +2311,7 @@
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>Marble Cheddar | $14.49</t>
+          <t>Chekn Brst Roast Ckd | $5.46</t>
         </is>
       </c>
     </row>
@@ -2915,26 +2322,15 @@
         </is>
       </c>
       <c r="B57" t="n">
-        <v>639</v>
+        <v>651</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Cheese Feta Light</t>
+          <t>Salami</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>6.99</v>
-      </c>
-      <c r="E57" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="F57" t="n">
-        <v>0</v>
-      </c>
-      <c r="G57" t="n">
-        <v>0</v>
+        <v>4.17</v>
       </c>
       <c r="H57" t="inlineStr">
         <is>
@@ -2943,12 +2339,12 @@
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>exact</t>
+          <t>default</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>Cheese Feta Light | $6.99</t>
+          <t>Salami | $4.17</t>
         </is>
       </c>
     </row>
@@ -2959,26 +2355,15 @@
         </is>
       </c>
       <c r="B58" t="n">
-        <v>643</v>
+        <v>655</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Chckn Brst Roast Ckd</t>
+          <t>Ferogies Potato&amp;Ched</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>5.46</v>
-      </c>
-      <c r="E58" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="F58" t="n">
-        <v>0</v>
-      </c>
-      <c r="G58" t="n">
-        <v>0</v>
+        <v>14.49</v>
       </c>
       <c r="H58" t="inlineStr">
         <is>
@@ -2987,12 +2372,12 @@
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>default</t>
+          <t>exact</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>Chekn Brst Roast Ckd | $5.46</t>
+          <t>Ferogies Potato&amp;Ched | $14.49</t>
         </is>
       </c>
     </row>
@@ -3003,26 +2388,15 @@
         </is>
       </c>
       <c r="B59" t="n">
-        <v>651</v>
+        <v>659</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Salami</t>
+          <t>Perogies Potato&amp;Ched</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>4.17</v>
-      </c>
-      <c r="E59" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="F59" t="n">
-        <v>0</v>
-      </c>
-      <c r="G59" t="n">
-        <v>0</v>
+        <v>7.49</v>
       </c>
       <c r="H59" t="inlineStr">
         <is>
@@ -3031,12 +2405,12 @@
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>default</t>
+          <t>exact</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>Salami | $4.17</t>
+          <t>Perogies Potato&amp;Ched | $7.49</t>
         </is>
       </c>
     </row>
@@ -3047,26 +2421,15 @@
         </is>
       </c>
       <c r="B60" t="n">
-        <v>655</v>
+        <v>665</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Perogies Potato&amp;Ched</t>
+          <t>Garlic Spread</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>14.49</v>
-      </c>
-      <c r="E60" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="F60" t="n">
-        <v>0</v>
-      </c>
-      <c r="G60" t="n">
-        <v>0</v>
+        <v>4.72</v>
       </c>
       <c r="H60" t="inlineStr">
         <is>
@@ -3075,12 +2438,12 @@
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>exact</t>
+          <t>default</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>Ferogies Potato&amp;Ched | $14.49</t>
+          <t>Garlic Spread | $4.72</t>
         </is>
       </c>
     </row>
@@ -3091,26 +2454,15 @@
         </is>
       </c>
       <c r="B61" t="n">
-        <v>659</v>
+        <v>669</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Perogies Potato&amp;Ched</t>
+          <t>Baguette White</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>7.49</v>
-      </c>
-      <c r="E61" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="F61" t="n">
-        <v>0</v>
-      </c>
-      <c r="G61" t="n">
-        <v>0</v>
+        <v>3.99</v>
       </c>
       <c r="H61" t="inlineStr">
         <is>
@@ -3119,12 +2471,12 @@
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>exact</t>
+          <t>ai_cache</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>Perogies Potato&amp;Ched | $7.49</t>
+          <t>Baguette White | $3.99</t>
         </is>
       </c>
     </row>
@@ -3135,26 +2487,15 @@
         </is>
       </c>
       <c r="B62" t="n">
-        <v>665</v>
+        <v>691</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Garlic Spread</t>
+          <t>ee a</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>4.72</v>
-      </c>
-      <c r="E62" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="F62" t="n">
-        <v>0</v>
-      </c>
-      <c r="G62" t="n">
-        <v>0</v>
+        <v>3.37</v>
       </c>
       <c r="H62" t="inlineStr">
         <is>
@@ -3168,183 +2509,7 @@
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>Garlic Spread | $4.72</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>20260214_sobeys_363_95</t>
-        </is>
-      </c>
-      <c r="B63" t="n">
-        <v>669</v>
-      </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>Baguette White</t>
-        </is>
-      </c>
-      <c r="D63" t="n">
-        <v>3.99</v>
-      </c>
-      <c r="E63" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="F63" t="n">
-        <v>0</v>
-      </c>
-      <c r="G63" t="n">
-        <v>0</v>
-      </c>
-      <c r="H63" t="inlineStr">
-        <is>
-          <t>Groceries</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr">
-        <is>
-          <t>ai_cache</t>
-        </is>
-      </c>
-      <c r="J63" t="inlineStr">
-        <is>
-          <t>Baguette White | $3.99</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>20260214_sobeys_363_95</t>
-        </is>
-      </c>
-      <c r="B64" t="n">
-        <v>673</v>
-      </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>Sausage Buns</t>
-        </is>
-      </c>
-      <c r="D64" t="n">
-        <v>5.49</v>
-      </c>
-      <c r="E64" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="F64" t="n">
-        <v>0</v>
-      </c>
-      <c r="G64" t="n">
-        <v>0</v>
-      </c>
-      <c r="H64" t="inlineStr">
-        <is>
-          <t>Groceries</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr">
-        <is>
-          <t>default</t>
-        </is>
-      </c>
-      <c r="J64" t="inlineStr">
-        <is>
-          <t>Sausage Buns | $5.49</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="inlineStr">
-        <is>
-          <t>20260214_sobeys_363_95</t>
-        </is>
-      </c>
-      <c r="B65" t="n">
-        <v>677</v>
-      </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>Buns Hot Dog</t>
-        </is>
-      </c>
-      <c r="D65" t="n">
-        <v>4.99</v>
-      </c>
-      <c r="E65" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="F65" t="n">
-        <v>0</v>
-      </c>
-      <c r="G65" t="n">
-        <v>0</v>
-      </c>
-      <c r="H65" t="inlineStr">
-        <is>
-          <t>Groceries</t>
-        </is>
-      </c>
-      <c r="I65" t="inlineStr">
-        <is>
-          <t>default</t>
-        </is>
-      </c>
-      <c r="J65" t="inlineStr">
-        <is>
-          <t>Buns Hot Dog | $4.99</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="inlineStr">
-        <is>
-          <t>20260214_sobeys_363_95</t>
-        </is>
-      </c>
-      <c r="B66" t="n">
-        <v>681</v>
-      </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>English Muffins Sour</t>
-        </is>
-      </c>
-      <c r="D66" t="n">
-        <v>3.49</v>
-      </c>
-      <c r="E66" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="F66" t="n">
-        <v>0</v>
-      </c>
-      <c r="G66" t="n">
-        <v>0</v>
-      </c>
-      <c r="H66" t="inlineStr">
-        <is>
-          <t>Groceries</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="J66" t="inlineStr">
-        <is>
-          <t>English Muffins Sour | $3.49</t>
+          <t>ee a | $3.37</t>
         </is>
       </c>
     </row>
@@ -3437,7 +2602,7 @@
         <v>363.95</v>
       </c>
       <c r="H2" t="n">
-        <v>71</v>
+        <v>61</v>
       </c>
     </row>
   </sheetData>
@@ -4092,7 +3257,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A6"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="60" customWidth="1" min="1" max="1"/>
@@ -4108,35 +3273,28 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Imported manual workbook: /Users/paul/Developer/home-budget-pipeline/sobeys_one.xlsx</t>
+          <t>Input path: /Users/paul/Developer/home-budget-pipeline/receipts/Sobeys</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Input path: /Users/paul/Developer/home-budget-pipeline/receipts/Sobeys</t>
+          <t>Receipts parsed: 1</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Receipts parsed: 1</t>
+          <t>Items parsed: 61</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Items parsed: 65</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>AI Status: enabled=True, disabled_runtime=False, calls=0, batch_items=0, ai_cache_hits=0, success=0, api_errors=0.</t>
+          <t>AI Status: enabled=True, disabled_runtime=False, calls=0, batch_items=0, ai_cache_hits=1, success=0, api_errors=0.</t>
         </is>
       </c>
     </row>
